--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -61,6 +64,12 @@
     <t>2026-05-15</t>
   </si>
   <si>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
+    <t>1925 HW Trakia, 243 km. Sofia direc</t>
+  </si>
+  <si>
     <t>СВ2394АО</t>
   </si>
   <si>
@@ -70,10 +79,19 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>09:28</t>
-  </si>
-  <si>
-    <t>09:06</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>09:26:00</t>
+  </si>
+  <si>
+    <t>09:06:00</t>
+  </si>
+  <si>
+    <t>3231864636 3231864636</t>
+  </si>
+  <si>
+    <t>3231929771 3231929771</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1</t>
@@ -497,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -506,16 +524,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -555,92 +574,101 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1195</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>35.31</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2">
         <v>1.65</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>58.26</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.8</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>63.56</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>230780</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1925</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>50.73</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3">
         <v>1.64</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>83.2</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.78</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>90.3</v>
       </c>
-      <c r="K3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>208364</v>
+      <c r="N3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -648,29 +676,29 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14">
       <c r="A7" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="A8" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B8" s="6">
         <v>86.04000000000001</v>
@@ -688,9 +716,9 @@
         <v>153.86</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:14">
       <c r="A9" s="8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B9" s="9">
         <v>86.04000000000001</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1.xlsx
@@ -145,7 +145,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -155,12 +155,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -210,17 +204,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,25 +46,13 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1195 243 Тракия Езеро</t>
-  </si>
-  <si>
-    <t>1925 HW Trakia, 243 km. Sofia direc</t>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>София Дружба 2</t>
   </si>
   <si>
     <t>СВ2394АО</t>
@@ -77,21 +62,6 @@
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>09:26:00</t>
-  </si>
-  <si>
-    <t>09:06:00</t>
-  </si>
-  <si>
-    <t>3231864636 3231864636</t>
-  </si>
-  <si>
-    <t>3231929771 3231929771</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1</t>
@@ -509,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -518,17 +488,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -562,175 +529,113 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2">
+        <v>52.47</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="H2">
+        <v>84.48</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="J2">
+        <v>83.95</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
-        <v>35.31</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="6">
+        <v>52.47</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1.6101</v>
+      </c>
+      <c r="E7" s="6">
+        <v>84.48</v>
+      </c>
+      <c r="F7" s="6">
+        <v>83.95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H2">
-        <v>1.65</v>
-      </c>
-      <c r="I2" s="1">
-        <v>58.26</v>
-      </c>
-      <c r="J2">
-        <v>1.8</v>
-      </c>
-      <c r="K2" s="1">
-        <v>63.56</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>50.73</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3">
-        <v>1.64</v>
-      </c>
-      <c r="I3" s="1">
-        <v>83.2</v>
-      </c>
-      <c r="J3">
-        <v>1.78</v>
-      </c>
-      <c r="K3" s="1">
-        <v>90.3</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="6">
-        <v>86.04000000000001</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1.6441</v>
-      </c>
-      <c r="E8" s="6">
-        <v>141.46</v>
-      </c>
-      <c r="F8" s="6">
-        <v>153.86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="9">
-        <v>86.04000000000001</v>
-      </c>
-      <c r="C9" s="9">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="9">
-        <v>141.46</v>
-      </c>
-      <c r="F9" s="9">
-        <v>153.86</v>
+      <c r="B8" s="9">
+        <v>52.47</v>
+      </c>
+      <c r="C8" s="9">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="9">
+        <v>84.48</v>
+      </c>
+      <c r="F8" s="9">
+        <v>83.95</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-15</t>
   </si>
   <si>
@@ -58,13 +67,16 @@
     <t>2026-06-17</t>
   </si>
   <si>
-    <t>София Дружба 2</t>
-  </si>
-  <si>
-    <t>Русе Дружба</t>
-  </si>
-  <si>
-    <t>АМ Тракия</t>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
+  </si>
+  <si>
+    <t>1172 Русе Шелф</t>
+  </si>
+  <si>
+    <t>1925 HW Trakia, 243 km. Sofia direc</t>
   </si>
   <si>
     <t>СВ2394АО</t>
@@ -76,13 +88,40 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-06-15 14:50:09</t>
-  </si>
-  <si>
-    <t>2026-06-16 11:47:06</t>
-  </si>
-  <si>
-    <t>2026-06-17 09:11:31</t>
+    <t>DIESEL DOUBLE FILTERED</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>14:50:00</t>
+  </si>
+  <si>
+    <t>11:47:00</t>
+  </si>
+  <si>
+    <t>09:11:00</t>
+  </si>
+  <si>
+    <t>11:36:00</t>
+  </si>
+  <si>
+    <t>05:22:00</t>
+  </si>
+  <si>
+    <t>3233391591 3233391591</t>
+  </si>
+  <si>
+    <t>3233439654 3233439654</t>
+  </si>
+  <si>
+    <t>3233484947 3233484947</t>
+  </si>
+  <si>
+    <t>3234051524 3234051524</t>
+  </si>
+  <si>
+    <t>3234048426 3234048426</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1</t>
@@ -500,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -509,14 +548,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -550,183 +592,327 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>52.47</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2">
         <v>1.55</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>81.33</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.6</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>83.95</v>
       </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>35.99</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3">
         <v>1.55</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>55.78</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.59</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>57.22</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F4">
         <v>45</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4">
         <v>1.54</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>69.3</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.61</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>72.45</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="3" t="s">
+      <c r="E5" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="4" t="s">
+      <c r="F5">
+        <v>38</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5">
+        <v>1.43</v>
+      </c>
+      <c r="I5" s="1">
+        <v>54.34</v>
+      </c>
+      <c r="J5">
+        <v>1.51</v>
+      </c>
+      <c r="K5" s="1">
+        <v>57.38</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="F6">
+        <v>30.03</v>
+      </c>
+      <c r="G6" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="6">
-        <v>133.46</v>
-      </c>
-      <c r="C9" s="6">
-        <v>3</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1.5466</v>
-      </c>
-      <c r="E9" s="6">
-        <v>206.41</v>
-      </c>
-      <c r="F9" s="6">
-        <v>213.62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="9">
-        <v>133.46</v>
-      </c>
-      <c r="C10" s="9">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="9">
-        <v>206.41</v>
-      </c>
-      <c r="F10" s="9">
-        <v>213.62</v>
+      <c r="H6">
+        <v>1.7</v>
+      </c>
+      <c r="I6" s="1">
+        <v>51.05</v>
+      </c>
+      <c r="J6">
+        <v>1.77</v>
+      </c>
+      <c r="K6" s="1">
+        <v>53.15</v>
+      </c>
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="6">
+        <v>171.46</v>
+      </c>
+      <c r="C11" s="6">
+        <v>4</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.5208</v>
+      </c>
+      <c r="E11" s="6">
+        <v>260.75</v>
+      </c>
+      <c r="F11" s="6">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="6">
+        <v>30.03</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1.7</v>
+      </c>
+      <c r="E12" s="6">
+        <v>51.05</v>
+      </c>
+      <c r="F12" s="6">
+        <v>53.15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="9">
+        <v>201.49</v>
+      </c>
+      <c r="C13" s="9">
+        <v>5</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="9">
+        <v>311.8</v>
+      </c>
+      <c r="F13" s="9">
+        <v>324.15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,10 +55,16 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-02</t>
   </si>
   <si>
-    <t>София Дружба 2</t>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
   </si>
   <si>
     <t>СВ2394АО</t>
@@ -67,7 +76,19 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-02 11:36:23</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:37:00</t>
+  </si>
+  <si>
+    <t>17:29:00</t>
+  </si>
+  <si>
+    <t>3234202214 3234202214</t>
+  </si>
+  <si>
+    <t>3234943780 3234943780</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1</t>
@@ -485,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -494,15 +515,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -539,116 +562,172 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>73.33</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2">
         <v>1.43</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>104.86</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.51</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>110.73</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="L2">
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>61.32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3">
+        <v>1.53</v>
+      </c>
+      <c r="I3" s="1">
+        <v>93.81999999999999</v>
+      </c>
+      <c r="J3">
+        <v>1.63</v>
+      </c>
+      <c r="K3" s="1">
+        <v>99.95</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="4" t="s">
+    <row r="7" spans="1:14">
+      <c r="A7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>9</v>
+      <c r="B8" s="6">
+        <v>134.65</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1.4755</v>
+      </c>
+      <c r="E8" s="6">
+        <v>198.68</v>
+      </c>
+      <c r="F8" s="6">
+        <v>210.68</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="6">
-        <v>73.33</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7">
-        <v>1.43</v>
-      </c>
-      <c r="E7" s="6">
-        <v>104.86</v>
-      </c>
-      <c r="F7" s="6">
-        <v>110.73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="9">
-        <v>73.33</v>
-      </c>
-      <c r="C8" s="9">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="9">
-        <v>104.86</v>
-      </c>
-      <c r="F8" s="9">
-        <v>110.73</v>
+    <row r="9" spans="1:14">
+      <c r="A9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="9">
+        <v>134.65</v>
+      </c>
+      <c r="C9" s="9">
+        <v>2</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="9">
+        <v>198.68</v>
+      </c>
+      <c r="F9" s="9">
+        <v>210.68</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1.xlsx
@@ -115,7 +115,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="7">
-        <v>1.4755</v>
+        <v>1.475529</v>
       </c>
       <c r="E8" s="6">
         <v>198.68</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -506,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -519,13 +522,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -568,98 +571,107 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2">
+        <v>73.331</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2">
+        <v>1.399</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.429</v>
+      </c>
+      <c r="J2">
+        <v>104.789999</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="L2" s="1">
+        <v>110.72981</v>
+      </c>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="F2">
-        <v>73.33</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="H2">
-        <v>1.43</v>
-      </c>
-      <c r="I2" s="1">
-        <v>104.86</v>
-      </c>
-      <c r="J2">
-        <v>1.51</v>
-      </c>
-      <c r="K2" s="1">
-        <v>110.73</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="F3">
+        <v>61.319</v>
+      </c>
+      <c r="G3" t="s">
         <v>21</v>
       </c>
-      <c r="M2">
+      <c r="H3">
+        <v>1.499</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.529</v>
+      </c>
+      <c r="J3">
+        <v>93.75675099999999</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="L3" s="1">
+        <v>99.94996999999999</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>23</v>
+      <c r="O3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3">
-        <v>61.32</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3">
-        <v>1.53</v>
-      </c>
-      <c r="I3" s="1">
-        <v>93.81999999999999</v>
-      </c>
-      <c r="J3">
-        <v>1.63</v>
-      </c>
-      <c r="K3" s="1">
-        <v>99.95</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="A6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -667,29 +679,29 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="6">
         <v>134.65</v>
@@ -698,18 +710,18 @@
         <v>2</v>
       </c>
       <c r="D8" s="7">
-        <v>1.475529</v>
+        <v>1.47454</v>
       </c>
       <c r="E8" s="6">
-        <v>198.68</v>
+        <v>198.55</v>
       </c>
       <c r="F8" s="6">
         <v>210.68</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="9">
         <v>134.65</v>
@@ -719,7 +731,7 @@
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="9">
-        <v>198.68</v>
+        <v>198.55</v>
       </c>
       <c r="F9" s="9">
         <v>210.68</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -117,8 +114,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -211,10 +208,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -522,13 +519,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -571,107 +568,98 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
       </c>
       <c r="F2">
         <v>73.331</v>
       </c>
       <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2">
+        <v>1.429</v>
+      </c>
+      <c r="I2" s="1">
+        <v>104.79</v>
+      </c>
+      <c r="J2">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="1">
+        <v>110.73</v>
+      </c>
+      <c r="L2" t="s">
         <v>21</v>
       </c>
-      <c r="H2">
-        <v>1.399</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.429</v>
-      </c>
-      <c r="J2">
-        <v>104.789999</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L2" s="1">
-        <v>110.72981</v>
-      </c>
-      <c r="M2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>24</v>
+      <c r="N2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
       </c>
       <c r="F3">
         <v>61.319</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I3" s="1">
-        <v>1.529</v>
+        <v>93.75700000000001</v>
       </c>
       <c r="J3">
-        <v>93.75675099999999</v>
+        <v>1.63</v>
       </c>
       <c r="K3" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L3" s="1">
-        <v>99.94996999999999</v>
-      </c>
-      <c r="M3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3">
+        <v>99.95</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -679,49 +667,49 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:14">
       <c r="A7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="A8" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="6">
         <v>134.65</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="7">
         <v>2</v>
       </c>
       <c r="D8" s="7">
-        <v>1.47454</v>
-      </c>
-      <c r="E8" s="6">
-        <v>198.55</v>
-      </c>
-      <c r="F8" s="6">
+        <v>1.475</v>
+      </c>
+      <c r="E8" s="7">
+        <v>198.547</v>
+      </c>
+      <c r="F8" s="7">
         <v>210.68</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="9">
         <v>134.65</v>
@@ -731,7 +719,7 @@
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="9">
-        <v>198.55</v>
+        <v>198.547</v>
       </c>
       <c r="F9" s="9">
         <v>210.68</v>
